--- a/datasets/Dataset_S7_Centrality_and_stability.xlsx
+++ b/datasets/Dataset_S7_Centrality_and_stability.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="357">
   <si>
     <t xml:space="preserve">Dataset S7. Centrality measures and Integrated Centrality of the regulators in the core GRN and the three species GRNs</t>
   </si>
@@ -72,10 +72,10 @@
     <t xml:space="preserve">Regulator name, where one is assigned (Dataset S5, Dataset S6-2).</t>
   </si>
   <si>
-    <t xml:space="preserve">stress_related, stress_category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Core GRN only: yes if a stress role is assigned (stress-coupled), and that role (Dataset S6-2).</t>
+    <t xml:space="preserve">stress_coupled, stress_category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Core GRN only: yes if a stress role is assigned, and that role (Dataset S6-2).</t>
   </si>
   <si>
     <t xml:space="preserve">degree</t>
@@ -123,7 +123,7 @@
     <t xml:space="preserve">*_seedmean, *_seedsd</t>
   </si>
   <si>
-    <t xml:space="preserve">Mean and standard deviation of the value across ten GENIE3 runs with fixed seeds, pruned as the network of record; a regulator absent from a run counts as 0.</t>
+    <t xml:space="preserve">Mean and standard deviation of the value across ten GENIE3 runs with fixed seeds, pruned as the representative network; a regulator absent from a run counts as 0.</t>
   </si>
   <si>
     <t xml:space="preserve">IC_rank</t>
@@ -138,7 +138,7 @@
     <t xml:space="preserve">(IC - IC_seedmean) / IC_seedsd.</t>
   </si>
   <si>
-    <t xml:space="preserve">stress_related</t>
+    <t xml:space="preserve">stress_coupled</t>
   </si>
   <si>
     <t xml:space="preserve">stress_category</t>
@@ -645,15 +645,9 @@
     <t xml:space="preserve">SGL_RS08210</t>
   </si>
   <si>
-    <t xml:space="preserve">dnaA</t>
-  </si>
-  <si>
     <t xml:space="preserve">SGL_RS03065</t>
   </si>
   <si>
-    <t xml:space="preserve">hrcA</t>
-  </si>
-  <si>
     <t xml:space="preserve">SGL_RS12005</t>
   </si>
   <si>
@@ -663,9 +657,6 @@
     <t xml:space="preserve">SGL_RS06215</t>
   </si>
   <si>
-    <t xml:space="preserve">nusG</t>
-  </si>
-  <si>
     <t xml:space="preserve">SGL_RS02990</t>
   </si>
   <si>
@@ -693,9 +684,6 @@
     <t xml:space="preserve">SGL_RS13130</t>
   </si>
   <si>
-    <t xml:space="preserve">nrdR</t>
-  </si>
-  <si>
     <t xml:space="preserve">SGL_RS15210</t>
   </si>
   <si>
@@ -720,13 +708,10 @@
     <t xml:space="preserve">SGL_RS02470</t>
   </si>
   <si>
-    <t xml:space="preserve">nusA</t>
-  </si>
-  <si>
     <t xml:space="preserve">SGL_RS08835</t>
   </si>
   <si>
-    <t xml:space="preserve">kaiC</t>
+    <t xml:space="preserve">KaiC2</t>
   </si>
   <si>
     <t xml:space="preserve">SGL_RS01625</t>
@@ -747,9 +732,6 @@
     <t xml:space="preserve">SGL_RS07730</t>
   </si>
   <si>
-    <t xml:space="preserve">sfsA</t>
-  </si>
-  <si>
     <t xml:space="preserve">SGL_RS13820</t>
   </si>
   <si>
@@ -768,9 +750,6 @@
     <t xml:space="preserve">SGL_RS15245</t>
   </si>
   <si>
-    <t xml:space="preserve">sufR</t>
-  </si>
-  <si>
     <t xml:space="preserve">SGL_RS11985</t>
   </si>
   <si>
@@ -780,9 +759,6 @@
     <t xml:space="preserve">SGL_RS14540</t>
   </si>
   <si>
-    <t xml:space="preserve">pyrR</t>
-  </si>
-  <si>
     <t xml:space="preserve">SGL_RS00670</t>
   </si>
   <si>
@@ -795,18 +771,12 @@
     <t xml:space="preserve">SGL_RS17245</t>
   </si>
   <si>
-    <t xml:space="preserve">rpoD</t>
-  </si>
-  <si>
     <t xml:space="preserve">SGL_RS15585</t>
   </si>
   <si>
     <t xml:space="preserve">SGL_RS14610</t>
   </si>
   <si>
-    <t xml:space="preserve">sigC</t>
-  </si>
-  <si>
     <t xml:space="preserve">SGL_RS17120</t>
   </si>
   <si>
@@ -858,9 +828,6 @@
     <t xml:space="preserve">SGL_RS11835</t>
   </si>
   <si>
-    <t xml:space="preserve">nusB</t>
-  </si>
-  <si>
     <t xml:space="preserve">SGL_RS08520</t>
   </si>
   <si>
@@ -1038,7 +1005,7 @@
     <t xml:space="preserve">SYNPCC7002_RS09260</t>
   </si>
   <si>
-    <t xml:space="preserve">lexA</t>
+    <t xml:space="preserve">LexA</t>
   </si>
   <si>
     <t xml:space="preserve">SYNPCC7002_RS14385</t>
@@ -12125,7 +12092,7 @@
         <v>208</v>
       </c>
       <c r="B15" t="s">
-        <v>209</v>
+        <v>64</v>
       </c>
       <c r="C15"/>
       <c r="D15"/>
@@ -12207,10 +12174,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B16" t="s">
-        <v>211</v>
+        <v>86</v>
       </c>
       <c r="C16"/>
       <c r="D16"/>
@@ -12292,10 +12259,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B17" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C17"/>
       <c r="D17"/>
@@ -12377,10 +12344,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s">
-        <v>215</v>
+        <v>82</v>
       </c>
       <c r="C18"/>
       <c r="D18"/>
@@ -12462,7 +12429,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B19"/>
       <c r="C19"/>
@@ -12545,10 +12512,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B20" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C20"/>
       <c r="D20"/>
@@ -12630,7 +12597,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B21"/>
       <c r="C21"/>
@@ -12713,10 +12680,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B22" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C22"/>
       <c r="D22"/>
@@ -12798,7 +12765,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B23"/>
       <c r="C23"/>
@@ -12881,7 +12848,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B24"/>
       <c r="C24"/>
@@ -12964,10 +12931,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B25" t="s">
-        <v>225</v>
+        <v>60</v>
       </c>
       <c r="C25"/>
       <c r="D25"/>
@@ -13049,7 +13016,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B26"/>
       <c r="C26"/>
@@ -13132,7 +13099,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B27"/>
       <c r="C27"/>
@@ -13215,7 +13182,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B28"/>
       <c r="C28"/>
@@ -13298,7 +13265,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B29"/>
       <c r="C29"/>
@@ -13381,10 +13348,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B30" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C30"/>
       <c r="D30"/>
@@ -13466,7 +13433,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B31"/>
       <c r="C31"/>
@@ -13549,10 +13516,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B32" t="s">
-        <v>234</v>
+        <v>101</v>
       </c>
       <c r="C32"/>
       <c r="D32"/>
@@ -13634,10 +13601,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B33" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C33"/>
       <c r="D33"/>
@@ -13719,7 +13686,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B34"/>
       <c r="C34"/>
@@ -13802,7 +13769,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B35"/>
       <c r="C35"/>
@@ -13885,7 +13852,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B36"/>
       <c r="C36"/>
@@ -13968,7 +13935,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B37"/>
       <c r="C37"/>
@@ -14051,7 +14018,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B38" t="s">
         <v>106</v>
@@ -14136,10 +14103,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B39" t="s">
-        <v>243</v>
+        <v>125</v>
       </c>
       <c r="C39"/>
       <c r="D39"/>
@@ -14221,7 +14188,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B40"/>
       <c r="C40"/>
@@ -14304,7 +14271,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B41"/>
       <c r="C41"/>
@@ -14387,7 +14354,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B42"/>
       <c r="C42"/>
@@ -14470,7 +14437,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B43"/>
       <c r="C43"/>
@@ -14553,7 +14520,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B44"/>
       <c r="C44"/>
@@ -14636,10 +14603,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B45" t="s">
-        <v>250</v>
+        <v>136</v>
       </c>
       <c r="C45"/>
       <c r="D45"/>
@@ -14721,7 +14688,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="B46"/>
       <c r="C46"/>
@@ -14804,7 +14771,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B47"/>
       <c r="C47"/>
@@ -14887,10 +14854,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="B48" t="s">
-        <v>254</v>
+        <v>123</v>
       </c>
       <c r="C48"/>
       <c r="D48"/>
@@ -14972,7 +14939,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B49"/>
       <c r="C49"/>
@@ -15055,7 +15022,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B50"/>
       <c r="C50"/>
@@ -15138,7 +15105,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="B51"/>
       <c r="C51"/>
@@ -15221,10 +15188,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="B52" t="s">
-        <v>259</v>
+        <v>113</v>
       </c>
       <c r="C52"/>
       <c r="D52"/>
@@ -15306,7 +15273,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="B53"/>
       <c r="C53"/>
@@ -15389,10 +15356,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="B54" t="s">
-        <v>262</v>
+        <v>127</v>
       </c>
       <c r="C54"/>
       <c r="D54"/>
@@ -15474,7 +15441,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="B55"/>
       <c r="C55"/>
@@ -15557,7 +15524,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="B56"/>
       <c r="C56"/>
@@ -15640,7 +15607,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="B57"/>
       <c r="C57"/>
@@ -15723,7 +15690,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B58"/>
       <c r="C58"/>
@@ -15806,7 +15773,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="B59"/>
       <c r="C59"/>
@@ -15889,7 +15856,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="B60"/>
       <c r="C60"/>
@@ -15972,7 +15939,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="B61"/>
       <c r="C61"/>
@@ -16055,7 +16022,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="B62"/>
       <c r="C62"/>
@@ -16138,7 +16105,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="B63"/>
       <c r="C63"/>
@@ -16221,7 +16188,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="B64"/>
       <c r="C64"/>
@@ -16304,7 +16271,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="B65"/>
       <c r="C65"/>
@@ -16387,7 +16354,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="B66"/>
       <c r="C66"/>
@@ -16470,7 +16437,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="B67"/>
       <c r="C67"/>
@@ -16553,7 +16520,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="B68"/>
       <c r="C68"/>
@@ -16636,7 +16603,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="B69"/>
       <c r="C69"/>
@@ -16719,7 +16686,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="B70"/>
       <c r="C70"/>
@@ -16802,10 +16769,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="B71" t="s">
-        <v>280</v>
+        <v>119</v>
       </c>
       <c r="C71"/>
       <c r="D71"/>
@@ -16887,7 +16854,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="B72"/>
       <c r="C72"/>
@@ -16970,7 +16937,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="B73"/>
       <c r="C73"/>
@@ -17053,7 +17020,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="B74"/>
       <c r="C74"/>
@@ -17236,7 +17203,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="B2" t="s">
         <v>91</v>
@@ -17321,7 +17288,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="B3" t="s">
         <v>82</v>
@@ -17406,7 +17373,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="B4" t="s">
         <v>193</v>
@@ -17491,7 +17458,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="B5" t="s">
         <v>129</v>
@@ -17576,7 +17543,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="B6" t="s">
         <v>96</v>
@@ -17661,10 +17628,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="B7" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="C7"/>
       <c r="D7"/>
@@ -17746,7 +17713,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="B8" t="s">
         <v>113</v>
@@ -17831,10 +17798,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="B9" t="s">
-        <v>225</v>
+        <v>60</v>
       </c>
       <c r="C9"/>
       <c r="D9"/>
@@ -17916,10 +17883,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="B10" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="C10"/>
       <c r="D10"/>
@@ -18001,7 +17968,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="B11" t="s">
         <v>119</v>
@@ -18086,10 +18053,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="B12" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="C12"/>
       <c r="D12"/>
@@ -18171,7 +18138,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="B13" t="s">
         <v>99</v>
@@ -18256,7 +18223,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="B14" t="s">
         <v>160</v>
@@ -18341,7 +18308,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
@@ -18424,7 +18391,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="B16" t="s">
         <v>111</v>
@@ -18509,7 +18476,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
@@ -18592,10 +18559,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="B18" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C18"/>
       <c r="D18"/>
@@ -18677,7 +18644,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="B19"/>
       <c r="C19"/>
@@ -18760,7 +18727,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="B20"/>
       <c r="C20"/>
@@ -18843,7 +18810,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="B21"/>
       <c r="C21"/>
@@ -18926,7 +18893,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="B22"/>
       <c r="C22"/>
@@ -19009,10 +18976,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="B23" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="C23"/>
       <c r="D23"/>
@@ -19094,7 +19061,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="B24"/>
       <c r="C24"/>
@@ -19177,7 +19144,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="B25"/>
       <c r="C25"/>
@@ -19260,10 +19227,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="B26" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="C26"/>
       <c r="D26"/>
@@ -19345,7 +19312,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="B27"/>
       <c r="C27"/>
@@ -19428,7 +19395,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="B28"/>
       <c r="C28"/>
@@ -19511,10 +19478,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="B29" t="s">
-        <v>211</v>
+        <v>86</v>
       </c>
       <c r="C29"/>
       <c r="D29"/>
@@ -19596,10 +19563,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="B30" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="C30"/>
       <c r="D30"/>
@@ -19681,7 +19648,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="B31"/>
       <c r="C31"/>
@@ -19764,7 +19731,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="B32" t="s">
         <v>115</v>
@@ -19849,7 +19816,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="B33"/>
       <c r="C33"/>
@@ -19932,7 +19899,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="B34"/>
       <c r="C34"/>
@@ -20015,7 +19982,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="B35"/>
       <c r="C35"/>
@@ -20098,10 +20065,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="B36" t="s">
-        <v>262</v>
+        <v>127</v>
       </c>
       <c r="C36"/>
       <c r="D36"/>
@@ -20183,7 +20150,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="B37"/>
       <c r="C37"/>
@@ -20266,7 +20233,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="B38"/>
       <c r="C38"/>
@@ -20349,7 +20316,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="B39"/>
       <c r="C39"/>
@@ -20432,7 +20399,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="B40"/>
       <c r="C40"/>
@@ -20515,7 +20482,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="B41"/>
       <c r="C41"/>
@@ -20598,7 +20565,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="B42"/>
       <c r="C42"/>
@@ -20681,7 +20648,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="B43"/>
       <c r="C43"/>
@@ -20764,7 +20731,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="B44" t="s">
         <v>152</v>
@@ -20849,7 +20816,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="B45"/>
       <c r="C45"/>
@@ -20932,7 +20899,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="B46"/>
       <c r="C46"/>
@@ -21015,7 +20982,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="B47"/>
       <c r="C47"/>
@@ -21098,10 +21065,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="B48" t="s">
-        <v>254</v>
+        <v>123</v>
       </c>
       <c r="C48"/>
       <c r="D48"/>
@@ -21183,10 +21150,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="B49" t="s">
-        <v>234</v>
+        <v>101</v>
       </c>
       <c r="C49"/>
       <c r="D49"/>
@@ -21268,7 +21235,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="B50"/>
       <c r="C50"/>
@@ -21351,10 +21318,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="B51" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="C51"/>
       <c r="D51"/>
@@ -21436,7 +21403,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="B52"/>
       <c r="C52"/>
@@ -21519,7 +21486,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="B53"/>
       <c r="C53"/>
@@ -21602,10 +21569,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="B54" t="s">
-        <v>209</v>
+        <v>64</v>
       </c>
       <c r="C54"/>
       <c r="D54"/>
@@ -21687,7 +21654,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="B55"/>
       <c r="C55"/>
@@ -21770,7 +21737,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="B56"/>
       <c r="C56"/>
@@ -21853,7 +21820,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="B57"/>
       <c r="C57"/>
@@ -21936,10 +21903,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="B58" t="s">
-        <v>243</v>
+        <v>125</v>
       </c>
       <c r="C58"/>
       <c r="D58"/>
@@ -22021,7 +21988,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="B59"/>
       <c r="C59"/>
@@ -22104,7 +22071,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="B60"/>
       <c r="C60"/>
@@ -22187,7 +22154,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="B61"/>
       <c r="C61"/>
@@ -22270,7 +22237,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="B62"/>
       <c r="C62"/>
@@ -22353,7 +22320,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="B63"/>
       <c r="C63"/>
@@ -22436,7 +22403,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="B64"/>
       <c r="C64"/>
@@ -22519,7 +22486,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="B65"/>
       <c r="C65"/>
@@ -22602,7 +22569,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="B66"/>
       <c r="C66"/>
@@ -22685,7 +22652,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="B67"/>
       <c r="C67"/>
@@ -22768,7 +22735,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="B68"/>
       <c r="C68"/>
@@ -22851,7 +22818,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="B69"/>
       <c r="C69"/>
@@ -22934,7 +22901,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="B70"/>
       <c r="C70"/>
@@ -23017,10 +22984,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="B71" t="s">
-        <v>250</v>
+        <v>136</v>
       </c>
       <c r="C71"/>
       <c r="D71"/>
@@ -23102,7 +23069,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="B72"/>
       <c r="C72"/>
@@ -23185,7 +23152,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="B73"/>
       <c r="C73"/>
@@ -23268,7 +23235,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="B74"/>
       <c r="C74"/>
@@ -23351,7 +23318,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="B75"/>
       <c r="C75"/>
@@ -23434,7 +23401,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="B76"/>
       <c r="C76"/>
@@ -23517,7 +23484,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="B77" t="s">
         <v>106</v>
@@ -23602,7 +23569,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="B78"/>
       <c r="C78"/>

--- a/datasets/Dataset_S7_Centrality_and_stability.xlsx
+++ b/datasets/Dataset_S7_Centrality_and_stability.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Regulator name, where one is assigned (Dataset S5, Dataset S6-2).</t>
   </si>
   <si>
-    <t xml:space="preserve">stress_coupled, stress_category</t>
+    <t xml:space="preserve">stress_related, stress_category</t>
   </si>
   <si>
     <t xml:space="preserve">Core GRN only: yes if a stress role is assigned, and that role (Dataset S6-2).</t>
@@ -138,7 +138,7 @@
     <t xml:space="preserve">(IC - IC_seedmean) / IC_seedsd.</t>
   </si>
   <si>
-    <t xml:space="preserve">stress_coupled</t>
+    <t xml:space="preserve">stress_related</t>
   </si>
   <si>
     <t xml:space="preserve">stress_category</t>
